--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-pr-bildgebung-radiologische-messung.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-pr-bildgebung-radiologische-messung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:44:38+00:00</t>
+    <t>2026-09-08T13:41:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-pr-bildgebung-radiologische-messung.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-pr-bildgebung-radiologische-messung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T13:41:14+00:00</t>
+    <t>2026-09-10T11:56:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-pr-bildgebung-radiologische-messung.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-pr-bildgebung-radiologische-messung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:56:08+00:00</t>
+    <t>2026-09-10T13:12:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-pr-bildgebung-radiologische-messung.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-pr-bildgebung-radiologische-messung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:12:52+00:00</t>
+    <t>2026-09-11T13:12:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-pr-bildgebung-radiologische-messung.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-pr-bildgebung-radiologische-messung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T13:12:48+00:00</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -990,6 +990,12 @@
     <t>sct</t>
   </si>
   <si>
+    <t>SNOMED CT Code</t>
+  </si>
+  <si>
+    <t>Ein Verweis auf einen von SNOMED CT definierten Code</t>
+  </si>
+  <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
   &lt;code value="122869004"/&gt;
@@ -1109,12 +1115,6 @@
   </si>
   <si>
     <t>Observation.code.coding:sct</t>
-  </si>
-  <si>
-    <t>SNOMED CT Code</t>
-  </si>
-  <si>
-    <t>Ein Verweis auf einen von SNOMED CT definierten Code</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -2012,7 +2012,7 @@
     <t>Bestandteile</t>
   </si>
   <si>
-    <t>Detailierte Bestandteile der Messung</t>
+    <t>detailierte Bestandteile der Beobachtung</t>
   </si>
   <si>
     <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -6757,10 +6757,10 @@
         <v>144</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>313</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>257</v>
@@ -6776,7 +6776,7 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>81</v>
@@ -6847,7 +6847,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>268</v>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>270</v>
@@ -7079,7 +7079,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>272</v>
@@ -7198,7 +7198,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>280</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>287</v>
@@ -7432,7 +7432,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>294</v>
@@ -7478,7 +7478,7 @@
         <v>81</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>81</v>
@@ -7549,7 +7549,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>302</v>
@@ -7668,10 +7668,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7697,16 +7697,16 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7755,7 +7755,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7776,7 +7776,7 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7787,14 +7787,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7819,13 +7819,13 @@
         <v>63</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7853,10 +7853,10 @@
         <v>156</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7874,7 +7874,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7889,27 +7889,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8021,10 +8021,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8138,10 +8138,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8255,10 +8255,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8370,10 +8370,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8487,10 +8487,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8606,10 +8606,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8723,10 +8723,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8840,10 +8840,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8957,10 +8957,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9076,10 +9076,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>311</v>
@@ -9107,10 +9107,10 @@
         <v>144</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>352</v>
+        <v>313</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>257</v>
@@ -9198,7 +9198,7 @@
         <v>355</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9313,7 +9313,7 @@
         <v>356</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9430,7 +9430,7 @@
         <v>357</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9549,7 +9549,7 @@
         <v>358</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9666,7 +9666,7 @@
         <v>359</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9783,7 +9783,7 @@
         <v>360</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9900,7 +9900,7 @@
         <v>361</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10045,16 +10045,16 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10103,7 +10103,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10124,7 +10124,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -10360,7 +10360,7 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>371</v>
@@ -13226,16 +13226,16 @@
         <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -13284,7 +13284,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13305,7 +13305,7 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
@@ -13702,10 +13702,10 @@
         <v>244</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>352</v>
+        <v>313</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>522</v>
@@ -14285,16 +14285,16 @@
         <v>105</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -14343,7 +14343,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14364,7 +14364,7 @@
         <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>81</v>
@@ -16633,16 +16633,16 @@
         <v>105</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
@@ -16691,7 +16691,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16712,7 +16712,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -18869,7 +18869,7 @@
         <v>649</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>81</v>
@@ -18897,10 +18897,10 @@
         <v>156</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>81</v>
@@ -18939,10 +18939,10 @@
         <v>650</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>81</v>
@@ -20151,16 +20151,16 @@
         <v>105</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>81</v>
@@ -20209,7 +20209,7 @@
         <v>81</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20230,7 +20230,7 @@
         <v>81</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>81</v>
